--- a/tableaux.xlsx
+++ b/tableaux.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louan\Documents\M1\S2\Technique de prévision et conjoncture\Dossier\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louan\Documents\M1\S2\Technique de prévision et conjoncture\Dossier\Technique_prev\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="97">
   <si>
     <t>Test de saisonnalité </t>
   </si>
@@ -193,6 +193,129 @@
   </si>
   <si>
     <t>SARIMA(3,1,1)   (0,1,2)12</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type </t>
+  </si>
+  <si>
+    <t>t-stat</t>
+  </si>
+  <si>
+    <t>AO</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Modèle</t>
+  </si>
+  <si>
+    <t>DM_stat</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>TBATS</t>
+  </si>
+  <si>
+    <t>-2.7049</t>
+  </si>
+  <si>
+    <t>0.0102</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>-2.6912</t>
+  </si>
+  <si>
+    <t>0.0105</t>
+  </si>
+  <si>
+    <t>ETS</t>
+  </si>
+  <si>
+    <t>-2.6787</t>
+  </si>
+  <si>
+    <t>0.0107</t>
+  </si>
+  <si>
+    <t>ADAM ETS</t>
+  </si>
+  <si>
+    <t>-2.6293</t>
+  </si>
+  <si>
+    <t>0.0117</t>
+  </si>
+  <si>
+    <t>Holt-Winters</t>
+  </si>
+  <si>
+    <t>-2.5884</t>
+  </si>
+  <si>
+    <t>0.0126</t>
+  </si>
+  <si>
+    <t>SARIMA</t>
+  </si>
+  <si>
+    <t>-2.5146</t>
+  </si>
+  <si>
+    <t>0.0144</t>
+  </si>
+  <si>
+    <t>STS</t>
+  </si>
+  <si>
+    <t>-2.3687</t>
+  </si>
+  <si>
+    <t>0.0186</t>
+  </si>
+  <si>
+    <t>X13-SARIMA-SEATS</t>
+  </si>
+  <si>
+    <t>-2.3180</t>
+  </si>
+  <si>
+    <t>0.0204</t>
+  </si>
+  <si>
+    <t>SSARIMA</t>
+  </si>
+  <si>
+    <t>-2.2816</t>
+  </si>
+  <si>
+    <t>0.0217</t>
+  </si>
+  <si>
+    <t>ADAM ETS + ARIMA</t>
+  </si>
+  <si>
+    <t>-2.1963</t>
+  </si>
+  <si>
+    <t>0.0252</t>
+  </si>
+  <si>
+    <t>Naïve</t>
+  </si>
+  <si>
+    <t>référence</t>
   </si>
 </sst>
 </file>
@@ -241,7 +364,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -264,18 +387,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -315,6 +461,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -353,12 +511,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tableau2" displayName="Tableau2" ref="L32:O33" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tableau2" displayName="Tableau2" ref="L32:O33" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <tableColumns count="4">
-    <tableColumn id="1" name="Level " dataDxfId="5"/>
-    <tableColumn id="2" name="Slope " dataDxfId="4"/>
-    <tableColumn id="3" name="Seas " dataDxfId="3"/>
-    <tableColumn id="4" name="Epsilon" dataDxfId="2"/>
+    <tableColumn id="1" name="Level " dataDxfId="3"/>
+    <tableColumn id="2" name="Slope " dataDxfId="2"/>
+    <tableColumn id="3" name="Seas " dataDxfId="1"/>
+    <tableColumn id="4" name="Epsilon" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -627,582 +785,763 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:O33"/>
+  <dimension ref="B2:X33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="15.453125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="15" width="15.453125" customWidth="1"/>
+    <col min="19" max="21" width="10.1796875" customWidth="1"/>
+    <col min="22" max="22" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="12.26953125" customWidth="1"/>
+    <col min="25" max="26" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="2:15" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I6" s="8" t="s">
+    <row r="2" spans="2:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="2:22" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="2:15" ht="28" x14ac:dyDescent="0.35">
-      <c r="B7" s="1" t="s">
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+    </row>
+    <row r="7" spans="2:22" ht="28" x14ac:dyDescent="0.35">
+      <c r="B7" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <v>1.5699999999999999E-2</v>
       </c>
-      <c r="M7" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="1" t="s">
+      <c r="M7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B8" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="3"/>
-      <c r="I8" s="7" t="s">
+      <c r="E8" s="16"/>
+      <c r="F8" s="2"/>
+      <c r="I8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="12">
+      <c r="J8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B9" s="2" t="s">
+      <c r="M8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="I9" s="7" t="s">
+      <c r="F9" s="2"/>
+      <c r="I9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <v>1E-4</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="11">
         <v>0.1704</v>
       </c>
-      <c r="M9" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="4">
+      <c r="M9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>0</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>72.23</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" s="12">
+      <c r="J10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="11">
         <v>0.98460000000000003</v>
       </c>
-      <c r="M10" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="I11" s="7" t="s">
+      <c r="M10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="I11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="11" t="s">
+      <c r="J11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="I12" s="7" t="s">
+      <c r="Q11" s="18">
+        <v>40026</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="S11" s="17">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="I12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="12">
+      <c r="J12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="11">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="11">
         <v>-1.0744</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="11">
         <v>-1.1109</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="11">
         <v>-1.4681</v>
       </c>
-      <c r="O12" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="I13" s="7" t="s">
+      <c r="O12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>43891</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="S12" s="17">
+        <v>-9.31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="I13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="12">
+      <c r="J13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="11">
         <v>-3.5200000000000002E-2</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="11">
         <v>-0.63739999999999997</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="11">
         <v>-0.44159999999999999</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="11">
         <v>-0.85460000000000003</v>
       </c>
-      <c r="O13" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="I14" s="7" t="s">
+      <c r="O13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>43922</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="S13" s="17">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="I14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" s="12">
+      <c r="J14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="11">
         <v>0.24529999999999999</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="11">
         <v>-5.2400000000000002E-2</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="11">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="11">
         <v>-0.22839999999999999</v>
       </c>
-      <c r="O14" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="I15" s="7" t="s">
+      <c r="O14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>44409</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="S14" s="17">
+        <v>-4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="I15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="12">
+      <c r="J15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="11">
         <v>4.2900000000000001E-2</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="11">
         <v>-1.46E-2</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="11">
         <v>0.5867</v>
       </c>
-      <c r="N15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="I16" s="7" t="s">
+      <c r="N15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="I16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="12">
+      <c r="J16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="11">
         <v>-0.12640000000000001</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="11">
         <v>-0.1048</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="11">
         <v>0.26910000000000001</v>
       </c>
-      <c r="N16" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I17" s="7" t="s">
+      <c r="N16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="12">
+      <c r="J17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="11">
         <v>-0.14990000000000001</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="11">
         <v>-0.75309999999999999</v>
       </c>
-      <c r="M17" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I18" s="7" t="s">
+      <c r="M17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L18" s="12">
+      <c r="J18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L18" s="11">
         <v>-0.4073</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="11">
         <v>0.49830000000000002</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="11">
         <v>0.95379999999999998</v>
       </c>
-      <c r="O18" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I19" s="7" t="s">
+      <c r="O18" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" s="12">
+      <c r="J19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19" s="11">
         <v>-0.44969999999999999</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="11">
         <v>-0.27379999999999999</v>
       </c>
-      <c r="N19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I20" s="7" t="s">
+      <c r="N19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L20" s="12">
+      <c r="J20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" s="11">
         <v>-0.1182</v>
       </c>
-      <c r="M20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I21" s="7" t="s">
+      <c r="M20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="V20" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W20" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="X20" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L21" s="12">
+      <c r="J21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L21" s="11">
         <v>0.17519999999999999</v>
       </c>
-      <c r="M21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N21" s="12">
+      <c r="M21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="11">
         <v>-0.69020000000000004</v>
       </c>
-      <c r="O21" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I22" s="7" t="s">
+      <c r="O21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="V21" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="W21" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="X21" s="21"/>
+    </row>
+    <row r="22" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="12">
+      <c r="J22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" s="11">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="M22" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" s="12">
+      <c r="M22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22" s="11">
         <v>-0.17399999999999999</v>
       </c>
-      <c r="O22" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I23" s="7" t="s">
+      <c r="O22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="V22" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="W22" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="X22" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L23" s="12">
+      <c r="J23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" s="11">
         <v>0.69120000000000004</v>
       </c>
-      <c r="M23" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I24" s="7" t="s">
+      <c r="M23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="V23" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="W23" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="X23" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="J24" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="M24" s="14" t="s">
+      <c r="M24" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="N24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O24" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I25" s="7" t="s">
+      <c r="N24" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="V24" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="W24" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="X24" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="11">
         <v>2616.0479999999998</v>
       </c>
-      <c r="M25" s="12">
+      <c r="M25" s="11">
         <v>2674.3290000000002</v>
       </c>
-      <c r="N25" s="12">
+      <c r="N25" s="11">
         <v>2476.66</v>
       </c>
-      <c r="O25" s="12">
+      <c r="O25" s="11">
         <v>3236.4589999999998</v>
       </c>
-    </row>
-    <row r="26" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I26" s="7" t="s">
+      <c r="V25" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="W25" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="X25" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="11">
         <v>2618.962</v>
       </c>
-      <c r="M26" s="12">
+      <c r="M26" s="11">
         <v>2674.9870000000001</v>
       </c>
-      <c r="N26" s="12">
+      <c r="N26" s="11">
         <v>2477.1999999999998</v>
       </c>
-      <c r="O26" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I32" s="6"/>
-      <c r="L32" s="16" t="s">
+      <c r="O26" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="V26" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="W26" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="X26" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="V27" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="W27" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="X27" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="V28" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="W28" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="X28" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="V29" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="W29" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="X29" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="V30" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="W30" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="X30" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="V31" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="W31" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="X31" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="9:24" x14ac:dyDescent="0.35">
+      <c r="I32" s="5"/>
+      <c r="L32" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M32" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="16" t="s">
+      <c r="N32" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="O32" s="16" t="s">
+      <c r="O32" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="33" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="L33" s="16" t="s">
+      <c r="L33" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="M33" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="N33" s="16" t="s">
+      <c r="N33" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="O33" s="16" t="s">
+      <c r="O33" s="15" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:E8"/>
+    <mergeCell ref="W21:X21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
